--- a/request_forms/044_notary_appointment_request_form--request_forms.xlsx
+++ b/request_forms/044_notary_appointment_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -874,12 +874,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>confirm_notary</t>
+          <t>confirm_notary_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Confirm Notary</t>
+          <t>Confirm Notary 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -897,12 +897,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>confirm_time</t>
+          <t>confirm_time_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Confirm Time</t>
+          <t>Confirm Time 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -920,12 +920,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>confirm_date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Confirm Date</t>
+          <t>Confirm Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>confirm_notary_choices</t>
+          <t>confirm_notary_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>confirm_notary_choices</t>
+          <t>confirm_notary_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>confirm_notary_choices</t>
+          <t>confirm_notary_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
